--- a/review-2026-10-30.xlsx
+++ b/review-2026-10-30.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N153"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,7 +605,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>reed:57482906</t>
+          <t>greenhouse:5378982008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -615,32 +615,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rest of UK</t>
+          <t>London &amp; around</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Trainee Digital Marketing Executive</t>
+          <t>Associate, Digital Operations - OOH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ITOL Recruit</t>
+          <t>WPP Media</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>£28,000–£38,000</t>
-        </is>
-      </c>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -650,12 +646,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/trainee-digital-marketing-executive/57482906</t>
+          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5378982008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -665,7 +661,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>greenhouse:5378982008</t>
+          <t>greenhouse:5189194008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -680,7 +676,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Associate, Digital Operations - OOH</t>
+          <t>Associate, Social</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -696,7 +692,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -711,7 +707,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5378982008</t>
+          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5189194008</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -721,7 +717,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>greenhouse:5189194008</t>
+          <t>greenhouse:5439637008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -736,7 +732,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Associate, Social</t>
+          <t>Campaign Executive</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -752,7 +748,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5189194008</t>
+          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5439637008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -777,7 +773,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>greenhouse:5439637008</t>
+          <t>workday:/job/London/Account-Executive_R1131060</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -792,23 +788,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Campaign Executive</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WPP Media</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -818,12 +814,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5439637008</t>
+          <t>https://dentsuaegis.wd3.myworkdayjobs.com/en-US/DAN_GLOBAL/job/London/Account-Executive_R1131060</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -833,7 +829,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>workday:/job/London/Account-Executive_R1131060</t>
+          <t>workday:/job/London/Client-Executive_R1130873</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -848,7 +844,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Client Executive</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -864,7 +860,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -879,7 +875,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://dentsuaegis.wd3.myworkdayjobs.com/en-US/DAN_GLOBAL/job/London/Account-Executive_R1131060</t>
+          <t>https://dentsuaegis.wd3.myworkdayjobs.com/en-US/DAN_GLOBAL/job/London/Client-Executive_R1130873</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -889,7 +885,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>workday:/job/London/Client-Executive_R1130873</t>
+          <t>workday:/job/London/Planning-Assistant_R1131933</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -904,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Client Executive</t>
+          <t>Planning Assistant</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -920,7 +916,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -935,7 +931,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://dentsuaegis.wd3.myworkdayjobs.com/en-US/DAN_GLOBAL/job/London/Client-Executive_R1130873</t>
+          <t>https://dentsuaegis.wd3.myworkdayjobs.com/en-US/DAN_GLOBAL/job/London/Planning-Assistant_R1131933</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -945,7 +941,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>workday:/job/London/Planning-Assistant_R1131933</t>
+          <t>workday:/job/London/Media-Executive_JR0100990-1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -960,12 +956,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Planning Assistant</t>
+          <t>Media Executive</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Havas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -976,7 +972,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -991,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://dentsuaegis.wd3.myworkdayjobs.com/en-US/DAN_GLOBAL/job/London/Planning-Assistant_R1131933</t>
+          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/Media-Executive_JR0100990-1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1001,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>workday:/job/London/Media-Executive_JR0100990-1</t>
+          <t>workday:/job/London/AV-Account-Executive_JR0100918</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1016,7 +1012,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Media Executive</t>
+          <t>AV Account Executive</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1032,7 +1028,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1047,7 +1043,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/Media-Executive_JR0100990-1</t>
+          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/AV-Account-Executive_JR0100918</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1057,7 +1053,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>workday:/job/London/AV-Account-Executive_JR0100918</t>
+          <t>workday:/job/London/Publishing-Account-Executive_JR0100353</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1072,7 +1068,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AV Account Executive</t>
+          <t>Publishing Account Executive</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1088,7 +1084,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1103,7 +1099,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/AV-Account-Executive_JR0100918</t>
+          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/Publishing-Account-Executive_JR0100353</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1113,7 +1109,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>workday:/job/London/Publishing-Account-Executive_JR0100353</t>
+          <t>workday:/job/London/Marketing---Events-Executive_JR0096373-1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1128,7 +1124,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Publishing Account Executive</t>
+          <t>Marketing &amp; Events Executive</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1144,7 +1140,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1159,7 +1155,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/Publishing-Account-Executive_JR0100353</t>
+          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/Marketing---Events-Executive_JR0096373-1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1169,7 +1165,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>workday:/job/London/Marketing---Events-Executive_JR0096373-1</t>
+          <t>workday:/job/London/ABM---Tech-Partnerships-Executive_JR0090103-2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Marketing &amp; Events Executive</t>
+          <t>ABM &amp; Tech Partnerships Executive</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1215,7 +1211,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/Marketing---Events-Executive_JR0096373-1</t>
+          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/ABM---Tech-Partnerships-Executive_JR0090103-2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1225,7 +1221,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>workday:/job/London/ABM---Tech-Partnerships-Executive_JR0090103-2</t>
+          <t>teamtailor:083ce943-e481-42c7-a1bf-4076a9e58b74</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1240,12 +1236,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ABM &amp; Tech Partnerships Executive</t>
+          <t>Digital Media Executive</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Havas</t>
+          <t>AKA UK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1256,7 +1252,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1266,12 +1262,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://wd3.myworkdaysite.com/recruiting/havas/GroupExternalCareerSite/job/London/ABM---Tech-Partnerships-Executive_JR0090103-2</t>
+          <t>https://careers.akauk.com/jobs/8630703-digital-media-executive</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1281,7 +1277,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>teamtailor:083ce943-e481-42c7-a1bf-4076a9e58b74</t>
+          <t>greenhouse:8882147002</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1296,17 +1292,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Digital Media Executive</t>
+          <t>UK Graduate Leadership Programme - Media Marketing Track (July Start)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AKA UK</t>
+          <t>Digital Voices</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>London, England, United Kingdom</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1322,12 +1318,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>teamtailor</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://careers.akauk.com/jobs/8630703-digital-media-executive</t>
+          <t>https://job-boards.greenhouse.io/pmg/jobs/8882147002</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1337,7 +1333,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>careers-page:https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest-browse_jobs</t>
+          <t>careers-page:https://www.fdry.com/careers/digital-marketing-executive/</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1352,12 +1348,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Account Executive jobs 71,457 open jobs</t>
+          <t>Digital Marketing Executive</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
+          <t>FDRY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1375,7 +1371,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest-browse_jobs</t>
+          <t>https://www.fdry.com/careers/digital-marketing-executive/</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1385,7 +1381,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>careers-page:https://www.linkedin.com/jobs/production-coordinator-jobs?trk=organization_guest-browse_jobs</t>
+          <t>careers-page:https://www.fdry.com/careers/account-executive/</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1400,12 +1396,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Production Coordinator jobs 20,645 open jobs</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
+          <t>FDRY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1423,7 +1419,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/production-coordinator-jobs?trk=organization_guest-browse_jobs</t>
+          <t>https://www.fdry.com/careers/account-executive/</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1433,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>careers-page:https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest_linkster_link</t>
+          <t>careers-page:https://kaizen.co.uk/careers/digital-pr-assistant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1448,12 +1444,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Account Executive jobs</t>
+          <t>Digital PR Assistant</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
+          <t>Kaizen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1471,7 +1467,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest_linkster_link</t>
+          <t>https://kaizen.co.uk/careers/digital-pr-assistant</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1481,7 +1477,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>careers-page:https://www.linkedin.com/jobs/marketing-assistant-jobs?trk=organization_guest_linkster_link</t>
+          <t>teamtailor:c6b3417c-a766-4e9f-a18e-a49d0d509e01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1496,17 +1492,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Marketing Assistant jobs</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>krow group</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1514,12 +1518,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/marketing-assistant-jobs?trk=organization_guest_linkster_link</t>
+          <t>https://themissiongroup-bray-leino-agency.teamtailor.com/jobs/8583110-account-executive</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1529,7 +1533,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>careers-page:https://www.linkedin.com/jobs/marketing-intern-jobs?trk=organization_guest_linkster_link</t>
+          <t>careers-page:https://www.tugagency.com/about-agency/careers/paid-media-account-executive/</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,12 +1548,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Marketing Intern jobs</t>
+          <t>Paid Media Account Executive</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
+          <t>Tug Agency</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1567,7 +1571,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/marketing-intern-jobs?trk=organization_guest_linkster_link</t>
+          <t>https://www.tugagency.com/about-agency/careers/paid-media-account-executive/</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1577,7 +1581,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>careers-page:https://www.linkedin.com/jobs/public-relations-account-executive-jobs?trk=organization_guest_linkster_link</t>
+          <t>careers-page:https://unity.online/careers/marketing-executive/</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1592,12 +1596,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Public Relations Account Executive jobs</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
+          <t>Unity Online</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1615,7 +1619,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/public-relations-account-executive-jobs?trk=organization_guest_linkster_link</t>
+          <t>https://unity.online/careers/marketing-executive/</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1625,7 +1629,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>careers-page:https://www.linkedin.com/jobs/assistant-producer-jobs?trk=organization_guest_linkster_link</t>
+          <t>teamtailor:b12cf74c-3316-4a42-8bb8-044bf6f23c17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1640,17 +1644,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Assistant Producer jobs</t>
+          <t>Junior Paid Media Consultant</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>Vervaunt</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1658,12 +1670,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/assistant-producer-jobs?trk=organization_guest_linkster_link</t>
+          <t>https://team.vervaunt.com/jobs/8464967-junior-paid-media-consultant</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1673,7 +1685,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>careers-page:https://www.linkedin.com/jobs/client-executive-jobs?trk=organization_guest_linkster_link</t>
+          <t>careers-page:https://wma.agency/careers/marketing-social-media-internship-ny/</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1688,12 +1700,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Client Executive jobs</t>
+          <t>Marketing &amp; Social Media Internship</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
+          <t>WMA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1711,7 +1723,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/client-executive-jobs?trk=organization_guest_linkster_link</t>
+          <t>https://wma.agency/careers/marketing-social-media-internship-ny/</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1721,7 +1733,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>greenhouse:8882147002</t>
+          <t>reed:57497958</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1736,23 +1748,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>UK Graduate Leadership Programme - Media Marketing Track (July Start)</t>
+          <t>Marketing Content Assistant</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Digital Voices</t>
+          <t>Handle Recruitment</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London, England, United Kingdom</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>£30,000–£35,000</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1762,12 +1778,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/pmg/jobs/8882147002</t>
+          <t>https://www.reed.co.uk/jobs/marketing-content-assistant/57497958</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1777,7 +1793,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>careers-page:https://www.fdry.com/careers/digital-marketing-executive/</t>
+          <t>reed:57497867</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1792,17 +1808,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive</t>
+          <t>Content Assistant</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FDRY</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+          <t>Michael Page Business Support</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Guildford</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>£28,000–£32,000</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1810,12 +1838,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.fdry.com/careers/digital-marketing-executive/</t>
+          <t>https://www.reed.co.uk/jobs/content-assistant/57497867</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1825,7 +1853,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>careers-page:https://www.fdry.com/careers/account-executive/</t>
+          <t>reed:57502657</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1840,17 +1868,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Digital Marketing Executive</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FDRY</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>Michael Page Digital</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1858,12 +1894,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.fdry.com/careers/account-executive/</t>
+          <t>https://www.reed.co.uk/jobs/digital-marketing-executive/57502657</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1873,7 +1909,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>careers-page:https://kaizen.co.uk/careers/digital-pr-assistant</t>
+          <t>reed:57473930</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1888,17 +1924,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Digital PR Assistant</t>
+          <t>Marketing Campaign Executive</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kaizen</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+          <t>The Portfolio Group</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>£32,000–£38,000</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1906,12 +1954,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://kaizen.co.uk/careers/digital-pr-assistant</t>
+          <t>https://www.reed.co.uk/jobs/marketing-campaign-executive/57473930</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1921,7 +1969,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>teamtailor:c6b3417c-a766-4e9f-a18e-a49d0d509e01</t>
+          <t>reed:57475904</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1936,12 +1984,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Performance Marketing Executive</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>krow group</t>
+          <t>Handle Recruitment</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1949,10 +1997,14 @@
           <t>London</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>£30,000–£35,000</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1962,12 +2014,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>teamtailor</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://themissiongroup-bray-leino-agency.teamtailor.com/jobs/8583110-account-executive</t>
+          <t>https://www.reed.co.uk/jobs/performance-marketing-executive/57475904</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -1977,7 +2029,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>careers-page:https://jobs.reachplc.com/job-description/id/744000157759180</t>
+          <t>reed:57503820</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1992,17 +2044,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Assistant Content Editor (News)</t>
+          <t>Social Media Executive</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reach Solutions</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+          <t>Sphere Digital Recruitment</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>£33,000–£37,000</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2010,12 +2074,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://jobs.reachplc.com/job-description/id/744000157759180</t>
+          <t>https://www.reed.co.uk/jobs/social-media-executive/57503820</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2025,7 +2089,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>careers-page:https://weareroast.com/careers/ppc-account-executive-2/</t>
+          <t>reed:57478149</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2040,17 +2104,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PPC Account Executive Cape Town Full Time Paid Media View role</t>
+          <t>Shopper Marketing Executive</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ROAST</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+          <t>Pursuit Resources Group</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>£32,000–£35,000</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2058,12 +2134,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://weareroast.com/careers/ppc-account-executive-2/</t>
+          <t>https://www.reed.co.uk/jobs/shopper-marketing-executive/57478149</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2073,7 +2149,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>careers-page:https://the-media-image.com/careers/graduate-program-paid-media-analyst-argentina/</t>
+          <t>reed:57498820</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2088,17 +2164,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Graduate Program: Paid Media Analyst (Argentina) Argentina Remote Paid Media Full Time Junior</t>
+          <t>E-Commerce Executive</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>The Media Image</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>Pursuit Resources Group</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2106,12 +2190,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://the-media-image.com/careers/graduate-program-paid-media-analyst-argentina/</t>
+          <t>https://www.reed.co.uk/jobs/e-commerce-executive/57498820</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2121,7 +2205,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>careers-page:https://the-media-image.com/careers/paid-media-associate-argentina/</t>
+          <t>reed:57500761</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2136,17 +2220,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paid Media Associate (Argentina) Argentina Remote Paid Media Full Time Junior-Mid</t>
+          <t>Amazon Marketplace and PPC Executive</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The Media Image</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+          <t>Get Staffed Online Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>£44,000–£47,000</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2154,12 +2250,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://the-media-image.com/careers/paid-media-associate-argentina/</t>
+          <t>https://www.reed.co.uk/jobs/amazon-marketplace-and-ppc-executive/57500761</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2169,7 +2265,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>careers-page:https://the-media-image.com/careers/graduate-programme-paid-media-analyst/</t>
+          <t>reed:57467709</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2184,17 +2280,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Graduate Programme: Paid Media Analyst (South Africa) SA Remote Paid Media Full Time Junior</t>
+          <t>Account Executive - Media - Hybrid</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>The Media Image</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+          <t>Aaron Wallis Sales Recruitment</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>West London</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>£35,000</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2202,12 +2310,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://the-media-image.com/careers/graduate-programme-paid-media-analyst/</t>
+          <t>https://www.reed.co.uk/jobs/account-executive-media-hybrid/57467709</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2217,7 +2325,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>careers-page:https://the-media-image.com/careers/junior-data-scientist/</t>
+          <t>reed:57487106</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2232,17 +2340,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Junior Data Scientist (United Kingdom) UK Hybrid Data Science &amp; Engineering Full Time Junior</t>
+          <t>PR and Communications Executive</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The Media Image</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+          <t>The Law Support Group</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>£40,000–£45,000</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2250,12 +2370,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://the-media-image.com/careers/junior-data-scientist/</t>
+          <t>https://www.reed.co.uk/jobs/pr-and-communications-executive/57487106</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2265,7 +2385,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>careers-page:https://weareroast.com/careers/ppc-account-executive-2/</t>
+          <t>reed:57476858</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2280,17 +2400,29 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PPC Account Executive Cape Town Full Time Paid Media View role</t>
+          <t>Graduate Marketing (CSA)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TIPi Group</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+          <t>Sphere Digital Recruitment</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>£38,000</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2298,12 +2430,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://weareroast.com/careers/ppc-account-executive-2/</t>
+          <t>https://www.reed.co.uk/jobs/graduate-marketing-csa/57476858</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2313,7 +2445,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>careers-page:https://www.tugagency.com/about-agency/careers/paid-media-account-executive/</t>
+          <t>adzuna:5934431056</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2328,17 +2460,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Media Account Executive</t>
+          <t>Marketing and Digital Assistant</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tug Agency</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>Handle Recruitment</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>South West London, London</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2346,12 +2486,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.tugagency.com/about-agency/careers/paid-media-account-executive/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5934431056?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2361,7 +2501,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>careers-page:https://unity.online/careers/marketing-executive/</t>
+          <t>adzuna:5939916419</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2376,17 +2516,29 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Marketing Executive</t>
+          <t>Italian Digital PR Assistant</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unity Online</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+          <t>The Opportunity Hub UK</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>£28,000–£30,000</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2394,12 +2546,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://unity.online/careers/marketing-executive/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5939916419?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2409,7 +2561,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>careers-page:https://upriseup.co.uk/careers/paid-media-executive/</t>
+          <t>adzuna:5936755442</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2424,17 +2576,29 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Paid Media Executive</t>
+          <t>Marketing Assistant</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+          <t>Taylor James Resourcing Limited</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>East London, London</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>£40,000</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2442,12 +2606,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://upriseup.co.uk/careers/paid-media-executive/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936755442?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2457,7 +2621,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>careers-page:https://upriseup.co.uk/careers/digital-media-data-assistant/</t>
+          <t>adzuna:5940270542</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2472,17 +2636,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Digital Media Data Assistant</t>
+          <t>Digital Marketing Executive</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>Ocuco</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gunnersbury, West London</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2490,12 +2662,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://upriseup.co.uk/careers/digital-media-data-assistant/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940270542?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2505,7 +2677,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>careers-page:https://upriseup.co.uk/careers/paid-digital-media-assistant/</t>
+          <t>adzuna:5945254837</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2520,17 +2692,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paid Digital Media Assistant</t>
+          <t>Digital Marketing Executive</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>Walr</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>North Lambeth, South East London</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2538,12 +2718,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://upriseup.co.uk/careers/paid-digital-media-assistant/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945254837?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2553,7 +2733,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>careers-page:https://upriseup.co.uk/careers/paid-digital-media-analyst/</t>
+          <t>adzuna:5938546986</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2568,17 +2748,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Paid Digital Media Analyst</t>
+          <t>Digital Marketing Executive, UK Digital Acquisition</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2586,12 +2774,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://upriseup.co.uk/careers/paid-digital-media-analyst/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546986?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2601,7 +2789,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>careers-page:https://upriseup.co.uk/careers/seo-assistant/</t>
+          <t>adzuna:5937070665</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2616,17 +2804,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SEO Assistant</t>
+          <t>Digital Marketing &amp; Content Executive</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>The Dorchester</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2634,12 +2830,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://upriseup.co.uk/careers/seo-assistant/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937070665?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2649,7 +2845,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>careers-page:https://upriseup.co.uk/careers/seo-analyst/</t>
+          <t>adzuna:5945448806</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2664,17 +2860,29 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SEO Analyst</t>
+          <t>Digital Marketing &amp; Content Executive</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+          <t>Dorchester Collection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mayfair, West London</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>£12,000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2682,12 +2890,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://upriseup.co.uk/careers/seo-analyst/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945448806?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2697,7 +2905,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>careers-page:https://www.version1.com/news/hm-land-registry-drives-forward-data-modernisation-programme-with-version-1/</t>
+          <t>adzuna:5935181643</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2712,17 +2920,29 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>News 21 September, 2026 HM Land Registry drives forward data modernisation programme with Version 1</t>
+          <t>Digital Marketing Analyst</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Version 1</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+          <t>The Opportunity Hub UK</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>£25,000–£30,000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2730,12 +2950,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.version1.com/news/hm-land-registry-drives-forward-data-modernisation-programme-with-version-1/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5935181643?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2745,7 +2965,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>teamtailor:b12cf74c-3316-4a42-8bb8-044bf6f23c17</t>
+          <t>adzuna:5936350462</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2760,23 +2980,23 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Junior Paid Media Consultant</t>
+          <t>Marketing Executive - Entertainment &amp; Live Experiences</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vervaunt</t>
+          <t>The Event Academy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2786,12 +3006,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>teamtailor</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://team.vervaunt.com/jobs/8464967-junior-paid-media-consultant</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936350462?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -2801,7 +3021,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>careers-page:https://wma.agency/careers/marketing-social-media-internship-ny/</t>
+          <t>adzuna:5943783539</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2816,17 +3036,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Marketing &amp; Social Media Internship</t>
+          <t>Content Marketing Executive</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>WMA</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>Grundon</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2834,12 +3062,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://wma.agency/careers/marketing-social-media-internship-ny/</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943783539?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -2849,7 +3077,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>reed:57500395</t>
+          <t>adzuna:5940234751</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2864,27 +3092,23 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Trainee Social Media Assistant</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Netcom Online Learning</t>
+          <t>Veriforce</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>£22,000–£28,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2894,12 +3118,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/trainee-social-media-assistant/57500395</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940234751?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -2909,7 +3133,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>reed:57500406</t>
+          <t>adzuna:5943403879</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2924,27 +3148,23 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Trainee Social Media Executive</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Netcom Online Learning</t>
+          <t>MarketFully</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>£22,000–£28,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2954,12 +3174,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/trainee-social-media-executive/57500406</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943403879?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -2969,7 +3189,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>reed:57500398</t>
+          <t>adzuna:5943655740</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2984,27 +3204,27 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Trainee Social Media Specialist</t>
+          <t>Social Media Executive</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Netcom Online Learning</t>
+          <t>Mumsnet</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Kentish Town, North West London</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>£22,000–£28,000</t>
+          <t>£32,000–£35,000</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3014,12 +3234,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/trainee-social-media-specialist/57500398</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943655740?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3029,7 +3249,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>reed:57497958</t>
+          <t>adzuna:5930230212</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3044,27 +3264,23 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Marketing Content Assistant</t>
+          <t>Global Social Media Executive</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Handle Recruitment</t>
+          <t>Collinson</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>£30,000–£35,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3074,12 +3290,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/marketing-content-assistant/57497958</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5930230212?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3089,7 +3305,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>reed:57497867</t>
+          <t>adzuna:5945456204</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3104,27 +3320,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Content Assistant</t>
+          <t>Social Media and Content Executive</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Michael Page Business Support</t>
+          <t>Dorchester Collection</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Mayfair, West London</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>£28,000–£32,000</t>
+          <t>£12,000</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3134,12 +3350,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/content-assistant/57497867</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945456204?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3149,7 +3365,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>reed:57479018</t>
+          <t>adzuna:5944487008</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3164,27 +3380,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Part Time Marketing &amp; Design Executive</t>
+          <t>Social Media &amp; Creative Content Executive</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Parkside Office Professional</t>
+          <t>The Hari</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Knightsbridge, South West London</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>£30,000–£35,000</t>
+          <t>£28,840</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3194,12 +3410,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/part-time-marketing-design-executive/57479018</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944487008?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3209,7 +3425,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>reed:57502657</t>
+          <t>adzuna:5936724448</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3224,23 +3440,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive</t>
+          <t>Brand Development Executive</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Michael Page Digital</t>
+          <t>Universal Business Team</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Sidcup, Kent</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>£35,000–£40,000</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3250,12 +3470,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/digital-marketing-executive/57502657</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936724448?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3265,7 +3485,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>reed:57473930</t>
+          <t>adzuna:5934293105</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3280,22 +3500,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Marketing Campaign Executive</t>
+          <t>Social Media Assistant</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>The Portfolio Group</t>
+          <t>Reed</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>£32,000–£38,000</t>
+          <t>£26,436</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3310,12 +3530,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/marketing-campaign-executive/57473930</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5934293105?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3325,7 +3545,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>reed:57475904</t>
+          <t>adzuna:5945446464</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3340,27 +3560,23 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Performance Marketing Executive</t>
+          <t>Social Media Assistant (UK)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Handle Recruitment</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>£30,000–£35,000</t>
-        </is>
-      </c>
+          <t>Chiswick, West London</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3370,12 +3586,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/performance-marketing-executive/57475904</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945446464?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3385,7 +3601,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>reed:57503820</t>
+          <t>adzuna:5937652834</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3400,27 +3616,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Social Media Executive</t>
+          <t>Social Media &amp; Community Management Assistant</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sphere Digital Recruitment</t>
+          <t>Nationwide</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>£33,000–£37,000</t>
-        </is>
-      </c>
+          <t>Liverpool Street, Central London</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3430,12 +3642,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/social-media-executive/57503820</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937652834?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3445,7 +3657,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>reed:57478149</t>
+          <t>adzuna:5938546255</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3460,27 +3672,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Shopper Marketing Executive</t>
+          <t>Social Video Intern</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pursuit Resources Group</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>£32,000–£35,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3490,12 +3698,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/shopper-marketing-executive/57478149</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546255?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3505,7 +3713,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>reed:57498820</t>
+          <t>adzuna:5938546249</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3520,23 +3728,23 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>E-Commerce Executive</t>
+          <t>Communications Intern (Universal Destinations &amp; Experiences)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pursuit Resources Group</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3546,12 +3754,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/e-commerce-executive/57498820</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546249?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3561,7 +3769,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>reed:57500761</t>
+          <t>adzuna:5944766327</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3576,24 +3784,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Amazon Marketplace and PPC Executive</t>
+          <t>Marketing Assistant</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Get Staffed Online Recruitment Limited</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>£44,000–£47,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3606,12 +3810,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/amazon-marketplace-and-ppc-executive/57500761</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944766327?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3621,7 +3825,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>reed:57467709</t>
+          <t>adzuna:5944934685</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3636,27 +3840,23 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Account Executive - Media - Hybrid</t>
+          <t>Performance Marketing Assistant</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aaron Wallis Sales Recruitment</t>
+          <t>Charles Tyrwhitt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>West London</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>£35,000</t>
-        </is>
-      </c>
+          <t>The City, Central London</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3666,12 +3866,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/account-executive-media-hybrid/57467709</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944934685?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3681,7 +3881,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>reed:57487106</t>
+          <t>adzuna:5937647997</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3696,27 +3896,23 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PR and Communications Executive</t>
+          <t>Talent &amp; Marketing Assistant</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>The Law Support Group</t>
+          <t>Hansen Filler Associates Limited</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>£40,000–£45,000</t>
-        </is>
-      </c>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3726,12 +3922,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/pr-and-communications-executive/57487106</t>
+          <t>https://www.adzuna.co.uk/jobs/land/ad/5937647997?se=mqPtf0bU8RGBsqu62qDD-w&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=9057C89125C435ECC44218FCA93AEB0B306255F5</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3741,7 +3937,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>reed:57480189</t>
+          <t>adzuna:5937651662</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3756,27 +3952,23 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Spanish and Japanese Sales Account Executive</t>
+          <t>Marketing Assistant EMEA - Shaw Contract</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>People First</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>South West London</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>£30,000–£40,000</t>
-        </is>
-      </c>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3786,12 +3978,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/spanish-and-japanese-sales-account-executive/57480189</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937651662?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3801,7 +3993,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>reed:57482672</t>
+          <t>adzuna:5937237472</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3816,24 +4008,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Account Executive - SAAS / Enterprise - B2B - Global Fintech Sector..</t>
+          <t>Marketing Assistant EMEA - Shaw Contract</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hawke Search </t>
+          <t>Shaw Industries Inc</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>£60,000–£72,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3846,12 +4034,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/account-executive-saas-enterprise-b2b-global-fintech-sector/57482672</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937237472?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -3861,7 +4049,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>reed:57487256</t>
+          <t>adzuna:5935270588</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3876,27 +4064,23 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>New Business Account Executive – MSPS, Outsourced Service, Integration Services, Service Based SaaS.</t>
+          <t>Email Marketing Operations Assistant</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Ltd</t>
+          <t>Decentralized Masters</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3906,12 +4090,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/new-business-account-executive--msps-outsourced-service-integration-services-service-based-saas/57487256</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5935270588?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -3921,7 +4105,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>reed:57476858</t>
+          <t>adzuna:5945753704</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3936,27 +4120,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Graduate Marketing (CSA)</t>
+          <t>Marketing and Communications Assistant</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sphere Digital Recruitment</t>
+          <t>Start People Ltd</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Hounslow, London</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>£38,000</t>
+          <t>£34,000–£37,000</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3966,12 +4150,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/graduate-marketing-csa/57476858</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945753704?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -3981,7 +4165,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>adzuna:5934431056</t>
+          <t>adzuna:5932702272</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3996,23 +4180,23 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Marketing and Digital Assistant</t>
+          <t>Marketing Intern - Rimmel</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Handle Recruitment</t>
+          <t>Coty</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>South West London, London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4027,7 +4211,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5934431056?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5932702272?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4037,7 +4221,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>adzuna:5940234757</t>
+          <t>adzuna:5940948225</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4052,12 +4236,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Assistant, Digital Sales and Marketing</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fifth Season</t>
+          <t>Coty</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4068,7 +4252,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4083,7 +4267,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940234757?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940948225?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4093,7 +4277,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>adzuna:5939916419</t>
+          <t>adzuna:5942771268</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4108,27 +4292,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Italian Digital PR Assistant</t>
+          <t>Travel Product and Marketing Executive</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The Opportunity Hub UK</t>
+          <t>Antella Travel Recruitment</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Aldwych, Central London</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>£28,000–£30,000</t>
+          <t>£34,000–£40,000</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4143,7 +4327,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5939916419?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5942771268?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4153,7 +4337,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>adzuna:5936755442</t>
+          <t>adzuna:5938360400</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4168,27 +4352,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Marketing Assistant</t>
+          <t>SEO Executive</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Taylor James Resourcing Limited</t>
+          <t>Additional Resources</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>East London, London</t>
+          <t>Leavesden, Watford</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£30,000–£35,000</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4203,7 +4387,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936755442?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938360400?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4213,7 +4397,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>adzuna:5940270542</t>
+          <t>adzuna:5936933181</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4228,23 +4412,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive</t>
+          <t>Content / SEO Assistant</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ocuco</t>
+          <t>Mandeville</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gunnersbury, West London</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>£32,000–£36,000</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4259,7 +4447,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940270542?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936933181?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4269,7 +4457,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>adzuna:5945254837</t>
+          <t>adzuna:5944530723</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4284,23 +4472,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive</t>
+          <t>Amazon Marketplace and PPC Executive</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Walr</t>
+          <t>AC Global</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>North Lambeth, South East London</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>£44,000–£47,000</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4315,7 +4507,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945254837?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944530723?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4325,7 +4517,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>adzuna:5938546986</t>
+          <t>adzuna:5940250032</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4340,23 +4532,23 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive, UK Digital Acquisition</t>
+          <t>Display &amp; Paid Social executive</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>IG Group</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>The City, Central London</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4371,7 +4563,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546986?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940250032?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4381,7 +4573,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>adzuna:5937070665</t>
+          <t>adzuna:5931858760</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4396,12 +4588,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Digital Marketing &amp; Content Executive</t>
+          <t>Biddable Executive (Paid Social &amp; Programmatic)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>The Dorchester</t>
+          <t>Havas</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4412,7 +4604,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4427,7 +4619,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937070665?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5931858760?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4437,7 +4629,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>adzuna:5945448806</t>
+          <t>adzuna:5936453313</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4452,27 +4644,23 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Digital Marketing &amp; Content Executive</t>
+          <t>Paid Media Executive</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dorchester Collection</t>
+          <t>Topdeck Travel</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mayfair, West London</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>£12,000</t>
-        </is>
-      </c>
+          <t>Gunnersbury, West London</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4487,7 +4675,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945448806?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936453313?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4497,7 +4685,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>adzuna:5931112462</t>
+          <t>adzuna:5944924185</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4512,12 +4700,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Agency New Business Executive (Digital Marketing)</t>
+          <t>Graduate Media Account Executive</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Awin</t>
+          <t>BrighterBox</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4525,10 +4713,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>£26,000</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4543,7 +4735,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931112462?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944924185?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4553,7 +4745,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>adzuna:5935181643</t>
+          <t>adzuna:5938296013</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4568,12 +4760,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Digital Marketing Analyst</t>
+          <t>Regional Digital Media &amp; Content Executive – UK &amp; EU</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>The Opportunity Hub UK</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4583,12 +4775,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>£25,000–£30,000</t>
+          <t>£36,837</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4603,7 +4795,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5935181643?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938296013?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4613,7 +4805,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>adzuna:5936350462</t>
+          <t>adzuna:5944336335</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4628,12 +4820,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Marketing Executive - Entertainment &amp; Live Experiences</t>
+          <t>Growth Marketing Executive</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>The Event Academy</t>
+          <t>Treatwell</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4641,10 +4833,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>£42,000</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4659,7 +4855,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936350462?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944336335?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4669,7 +4865,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>adzuna:5943783539</t>
+          <t>adzuna:5946683887</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4684,23 +4880,23 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Content Marketing Executive</t>
+          <t>PR &amp; Communications Executive</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Grundon</t>
+          <t>Collinson</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Slough, Berkshire</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4715,7 +4911,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943783539?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5946683887?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4725,7 +4921,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>adzuna:5940234751</t>
+          <t>adzuna:5945458765</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4740,12 +4936,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Marketing Executive</t>
+          <t>Account Executive, Influencer Marketing</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Veriforce</t>
+          <t>Acceleration Partners</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4753,10 +4949,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>£27,000–£37,000</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4771,7 +4971,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940234751?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945458765?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4781,7 +4981,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>adzuna:5936270512</t>
+          <t>adzuna:5934032852</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4796,23 +4996,23 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Trading Performance Analyst - Hospitals &amp; Primary Care</t>
+          <t>Strategic Account Executive</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nuffield Health</t>
+          <t>Pilot Thomas Logistics</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ewell, Epsom</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4827,7 +5027,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936270512?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5934032852?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4837,7 +5037,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>adzuna:5940251788</t>
+          <t>adzuna:5944530692</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4852,27 +5052,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CIBSE Certification Marketing Executive</t>
+          <t>Content Executive</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cibse</t>
+          <t>Auxo Future Build</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Finchley, North London</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>£33,000</t>
+          <t>£26,500–£27,000</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4887,7 +5087,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940251788?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944530692?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -4897,7 +5097,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>adzuna:5943403879</t>
+          <t>adzuna:5938546221</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4912,12 +5112,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Acquired Content Distribution Strategy Intern</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MarketFully</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4928,7 +5128,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4943,7 +5143,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943403879?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546221?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -4953,7 +5153,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>adzuna:5943655740</t>
+          <t>adzuna:5938546260</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4968,27 +5168,23 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Social Media Executive</t>
+          <t>Corporate Communications Intern</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mumsnet</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kentish Town, North West London</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>£32,000–£35,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5003,7 +5199,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943655740?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546260?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5013,7 +5209,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>adzuna:5930230212</t>
+          <t>adzuna:5939000242</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5028,12 +5224,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Global Social Media Executive</t>
+          <t>Business Marketing Operations Associate - Publishing</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Collinson</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5044,7 +5240,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5059,7 +5255,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930230212?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/land/ad/5939000242?se=8gxJgUbU8RGQ-s1xb079dA&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=E765009762CC63ACAF94DF3F47D207C928022DA1</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5069,7 +5265,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>adzuna:5938299681</t>
+          <t>adzuna:5937111775</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5084,20 +5280,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Social Media Executive - Training Course</t>
+          <t>Digital Coordinator</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Netcom Training</t>
+          <t>Office Angels</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Farringdon, Central London</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>Covent Garden, Central London</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>£29,000–£31,000</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -5115,7 +5315,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938299681?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937111775?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5125,7 +5325,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>adzuna:5939062483</t>
+          <t>adzuna:5939062485</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5140,12 +5340,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Freelance Social Media &amp; Marketing Executive</t>
+          <t>Content Executive</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>StudioXAG</t>
+          <t>re:act marketing ltd</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5153,11 +5353,7 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>£140–£200</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>2026-10-23</t>
@@ -5175,7 +5371,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5939062483?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5939062485?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5185,7 +5381,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>adzuna:5945456204</t>
+          <t>adzuna:5944670547</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5200,27 +5396,23 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Social Media and Content Executive</t>
+          <t>Community Executive</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dorchester Collection</t>
+          <t>Founders Forum Group</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mayfair, West London</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>£12,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5235,7 +5427,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945456204?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944670547?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5245,7 +5437,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>adzuna:5944487008</t>
+          <t>adzuna:5938546239</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5260,27 +5452,23 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Social Media &amp; Creative Content Executive</t>
+          <t>Audience Insights &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>The Hari</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knightsbridge, South West London</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>£28,840</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5295,7 +5483,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944487008?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546239?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5305,7 +5493,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>adzuna:5936724448</t>
+          <t>adzuna:5935226000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5320,27 +5508,23 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Brand Development Executive</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Universal Business Team</t>
+          <t>Dr. Martens</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sidcup, Kent</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>£35,000–£40,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5355,7 +5539,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936724448?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5935226000?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5365,7 +5549,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>adzuna:5934293105</t>
+          <t>adzuna:5931392610</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5380,27 +5564,23 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Social Media Assistant</t>
+          <t>Communications Associate - SAP UK Intern (13 Month Placement)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Reed</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>£26,436</t>
-        </is>
-      </c>
+          <t>Feltham, London</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5415,7 +5595,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5934293105?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5931392610?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5425,7 +5605,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>adzuna:5945446464</t>
+          <t>adzuna:5938546236</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5440,23 +5620,23 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Social Media Assistant (UK)</t>
+          <t>Content Planning &amp; Acquisitions Intern</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chiswick, West London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5471,7 +5651,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945446464?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546236?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5481,7 +5661,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>adzuna:5937652834</t>
+          <t>adzuna:5946686259</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5496,23 +5676,23 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Social Media &amp; Community Management Assistant</t>
+          <t>UK Graduate Leadership Programme - Media Marketing Track (July Start)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nationwide</t>
+          <t>PMG</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liverpool Street, Central London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5527,7 +5707,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937652834?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5946686259?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5537,7 +5717,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>adzuna:5938546255</t>
+          <t>adzuna:5930241938</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5552,12 +5732,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Social Video Intern</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>Stelia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5565,10 +5745,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>£28,000</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5583,7 +5767,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546255?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5930241938?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5593,7 +5777,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>adzuna:5945045489</t>
+          <t>adzuna:5943453576</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5608,23 +5792,23 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Interim Marketing Coordinator</t>
+          <t>Marketing Apprentice</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Frasers Hospitality</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>South Kensington, South West London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5639,7 +5823,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945045489?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943453576?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5649,7 +5833,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>adzuna:5938546249</t>
+          <t>adzuna:5930276586</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5664,12 +5848,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Communications Intern (Universal Destinations &amp; Experiences)</t>
+          <t>Lifecycle Marketing Intern</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>Teya</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5680,7 +5864,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5695,7 +5879,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546249?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5930276586?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5705,7 +5889,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>adzuna:5944766327</t>
+          <t>adzuna:5938546231</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5720,12 +5904,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Marketing Assistant</t>
+          <t>Trade Marketing Intern</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5736,7 +5920,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5751,7 +5935,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944766327?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546231?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5761,7 +5945,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>adzuna:5944934685</t>
+          <t>adzuna:5940073573</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5776,23 +5960,23 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Performance Marketing Assistant</t>
+          <t>AI &amp; Digital Marketing Apprentice</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Charles Tyrwhitt</t>
+          <t>Hollywood Bowl Group</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>The City, Central London</t>
+          <t>Hemel Hempstead, Hertfordshire</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5807,7 +5991,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944934685?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940073573?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5817,7 +6001,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>adzuna:5937647997</t>
+          <t>adzuna:5931144491</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5832,23 +6016,23 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Talent &amp; Marketing Assistant</t>
+          <t>BBM UK Marketing Intern</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hansen Filler Associates Limited</t>
+          <t>Bosch Group</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Farringdon, Central London</t>
+          <t>Denham, Buckinghamshire</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5863,7 +6047,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/land/ad/5937647997?se=2Ahzs0TU8RG_r4bmUg0vXw&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=9057C89125C435ECC44218FCA93AEB0B306255F5</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5931144491?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5873,7 +6057,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>adzuna:5936932882</t>
+          <t>adzuna:5938546235</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5888,27 +6072,23 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Temporary Marketing Assistant</t>
+          <t>Franchise Marketing Intern (Consumer Products)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Michael Page</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hounslow, London</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>£27,040–£31,200</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5923,7 +6103,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936932882?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546235?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -5933,7 +6113,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>adzuna:5930698734</t>
+          <t>adzuna:5945463670</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5948,27 +6128,23 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Trainee Sales &amp; Marketing Assistant</t>
+          <t>Intern, Brand Marketing &amp; Media EMEAI</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Horizon</t>
+          <t>Tapestry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>South East London, London</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>£30,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5983,7 +6159,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930698734?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945463670?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -5993,7 +6169,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>adzuna:5934612226</t>
+          <t>adzuna:5944311957</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6008,23 +6184,23 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Marketing Assistant - No Experience Required</t>
+          <t>Spring 2027 - Intern, Brand Marketing (London)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Growth for Good</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>West London, London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6039,7 +6215,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5934612226?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944311957?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6049,7 +6225,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>adzuna:5937651662</t>
+          <t>adzuna:5929514476</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6064,23 +6240,23 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Marketing Assistant EMEA - Shaw Contract</t>
+          <t>Marketing Associate - SAP UK Intern (13 Month Placement)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>SAP IT Business Systeme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Farringdon, Central London</t>
+          <t>Feltham, London</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6095,7 +6271,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937651662?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5929514476?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6105,7 +6281,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>adzuna:5937237472</t>
+          <t>adzuna:5931392619</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6120,23 +6296,23 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Marketing Assistant EMEA - Shaw Contract</t>
+          <t>Marketing Associate - SAP UK Intern (13 Month Placement)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shaw Industries Inc</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Feltham, London</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6151,7 +6327,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937237472?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5931392619?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6161,7 +6337,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>adzuna:5935270588</t>
+          <t>adzuna:5940948234</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6176,12 +6352,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Email Marketing Operations Assistant</t>
+          <t>PR and Communications Intern</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Decentralized Masters</t>
+          <t>Coty</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6192,7 +6368,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6207,7 +6383,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5935270588?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940948234?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6217,7 +6393,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>adzuna:5945753704</t>
+          <t>adzuna:5943784221</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6232,27 +6408,27 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Marketing and Communications Assistant</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Start People Ltd</t>
+          <t>Morson Edge</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hounslow, London</t>
+          <t>South West London, London</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>£34,000–£37,000</t>
+          <t>£30,000</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6267,7 +6443,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945753704?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943784221?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6277,7 +6453,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>adzuna:5932702272</t>
+          <t>adzuna:5940221334</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6292,23 +6468,23 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Marketing Intern - Rimmel</t>
+          <t>PR Intern</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Coty</t>
+          <t>Glassworks London</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Haggerston, East London</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6323,7 +6499,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5932702272?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/land/ad/5940221334?se=QC6xgUbU8RG_r4bmUg0vXw&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=2A631FA1C5085882063025A857E0FF695C7F8AC1</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6333,7 +6509,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>adzuna:5940948225</t>
+          <t>adzuna:5946684470</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6348,12 +6524,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Marketing &amp; Events Coordinator</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Coty</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6361,10 +6537,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>£44,000–£55,000</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6379,7 +6559,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940948225?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5946684470?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6389,7 +6569,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>adzuna:5942771268</t>
+          <t>adzuna:5930951195</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6404,27 +6584,23 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Travel Product and Marketing Executive</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Antella Travel Recruitment</t>
+          <t>V-Nova</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Aldwych, Central London</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>£34,000–£40,000</t>
-        </is>
-      </c>
+          <t>Paddington, West London</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6439,2524 +6615,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5942771268?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5930951195?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>adzuna:5938360400</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>SEO Executive</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Additional Resources</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Leavesden, Watford</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>£30,000–£35,000</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938360400?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>adzuna:5936933181</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Content / SEO Assistant</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Mandeville</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Farringdon, Central London</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>£32,000–£36,000</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936933181?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>adzuna:5944530723</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Amazon Marketplace and PPC Executive</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AC Global</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>£44,000–£47,000</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944530723?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>adzuna:5940250032</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Display &amp; Paid Social executive</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>IG Group</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>The City, Central London</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940250032?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>adzuna:5931858760</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Biddable Executive (Paid Social &amp; Programmatic)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Havas</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931858760?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>adzuna:5936453313</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Paid Media Executive</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Topdeck Travel</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Gunnersbury, West London</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936453313?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>adzuna:5944924185</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Graduate Media Account Executive</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>BrighterBox</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>£26,000</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944924185?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>adzuna:5942325792</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Account Executive, Media Sales</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Blis</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Southwark, South East London</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5942325792?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>adzuna:5938296013</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Regional Digital Media &amp; Content Executive – UK &amp; EU</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>COYA</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>£36,837</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938296013?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>adzuna:5937643216</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>New Business Executive at United Media</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>United Media</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937643216?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>adzuna:5944336335</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Growth Marketing Executive</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Treatwell</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>£42,000</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944336335?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>adzuna:5946683887</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>PR &amp; Communications Executive</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Collinson</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5946683887?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>adzuna:5945458765</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Account Executive, Influencer Marketing</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Acceleration Partners</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>£27,000–£37,000</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945458765?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>adzuna:5931443469</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Marketing Executive (12M Fixed Term Contract)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Enra Specialist Finance</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Leavesden, Watford</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931443469?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>adzuna:5934032852</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Strategic Account Executive</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Pilot Thomas Logistics</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5934032852?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>adzuna:5944530692</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Content Executive</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Auxo Future Build</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Finchley, North London</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>£26,500–£27,000</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944530692?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>adzuna:5938546221</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Acquired Content Distribution Strategy Intern</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>NBC Universal</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546221?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>adzuna:5938546260</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Corporate Communications Intern</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>NBC Universal</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546260?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>adzuna:5939000242</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Business Marketing Operations Associate - Publishing</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/land/ad/5939000242?se=OkDstETU8RGBsqu62qDD-w&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=E765009762CC63ACAF94DF3F47D207C928022DA1</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>adzuna:5937111775</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Digital Coordinator</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Office Angels</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Covent Garden, Central London</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>£29,000–£31,000</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937111775?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>adzuna:5939062485</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Content Executive</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>re:act marketing ltd</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5939062485?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>adzuna:5944670547</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Community Executive</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Founders Forum Group</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944670547?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>adzuna:5938546239</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Audience Insights &amp; Analytics Intern</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>NBC Universal</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546239?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>adzuna:5935226000</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Social Media Coordinator</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Dr. Martens</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5935226000?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>adzuna:5931392610</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Communications Associate - SAP UK Intern (13 Month Placement)</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Feltham, London</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931392610?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>adzuna:5938546236</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Content Planning &amp; Acquisitions Intern</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>NBC Universal</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546236?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>adzuna:5946686259</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>UK Graduate Leadership Programme - Media Marketing Track (July Start)</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>PMG</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5946686259?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>adzuna:5930241938</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Marketing Intern</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Stelia</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>£28,000</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930241938?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>adzuna:5943453576</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Marketing Apprentice</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943453576?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>adzuna:5930276586</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Lifecycle Marketing Intern</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Teya</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930276586?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>adzuna:5938546231</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Trade Marketing Intern</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>NBC Universal</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546231?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>adzuna:5940073573</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>AI &amp; Digital Marketing Apprentice</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Hollywood Bowl Group</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Hemel Hempstead, Hertfordshire</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940073573?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>adzuna:5931144491</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>BBM UK Marketing Intern</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Bosch Group</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Denham, Buckinghamshire</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931144491?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>adzuna:5938546235</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Franchise Marketing Intern (Consumer Products)</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>NBC Universal</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546235?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>adzuna:5936256509</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>PT Data Analysis &amp; Marketing/Sales Intern</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Bosch Group</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Denham, Buckinghamshire</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936256509?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>adzuna:5945463670</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Intern, Brand Marketing &amp; Media EMEAI</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Tapestry</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945463670?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>adzuna:5944311957</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Spring 2027 - Intern, Brand Marketing (London)</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Excel Sports Management</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944311957?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>adzuna:5929514476</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Marketing Associate - SAP UK Intern (13 Month Placement)</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>SAP IT Business Systeme</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Feltham, London</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5929514476?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>adzuna:5931392619</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Marketing Associate - SAP UK Intern (13 Month Placement)</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Feltham, London</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931392619?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>adzuna:5940948234</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>PR and Communications Intern</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Coty</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940948234?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>adzuna:5943784221</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Marketing Executive</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Morson Edge</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>South West London, London</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>£30,000</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943784221?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>adzuna:5940221334</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>PR Intern</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Glassworks London</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Haggerston, East London</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/land/ad/5940221334?se=5HhUtUTU8RGaYZOywuySTw&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=2A631FA1C5085882063025A857E0FF695C7F8AC1</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>adzuna:5946684470</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Events Coordinator</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Handshake</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>£44,000–£55,000</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5946684470?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>adzuna:5930951195</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>London &amp; around</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Marketing Executive</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>V-Nova</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Paddington, West London</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930951195?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8969,7 +6633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8991,6 +6655,952 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>First seen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Account Executive jobs 71,457 open jobs</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bountiful Cow</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Production Coordinator jobs 20,645 open jobs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bountiful Cow</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/production-coordinator-jobs?trk=organization_guest-browse_jobs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Account Executive jobs</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bountiful Cow</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest_linkster_link</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Marketing Assistant jobs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bountiful Cow</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/marketing-assistant-jobs?trk=organization_guest_linkster_link</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Marketing Intern jobs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bountiful Cow</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/marketing-intern-jobs?trk=organization_guest_linkster_link</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Public Relations Account Executive jobs</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bountiful Cow</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/public-relations-account-executive-jobs?trk=organization_guest_linkster_link</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Assistant Producer jobs</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bountiful Cow</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/assistant-producer-jobs?trk=organization_guest_linkster_link</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Client Executive jobs</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bountiful Cow</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/client-executive-jobs?trk=organization_guest_linkster_link</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Assistant Content Editor (News)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Reach Solutions</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://jobs.reachplc.com/job-description/id/744000157759180</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PPC Account Executive Cape Town Full Time Paid Media View role</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TIPi Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://weareroast.com/careers/ppc-account-executive-2/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Graduate Program: Paid Media Analyst (Argentina) Argentina Remote Paid Media Full Time Junior</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Media Image</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://the-media-image.com/careers/graduate-program-paid-media-analyst-argentina/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Paid Media Associate (Argentina) Argentina Remote Paid Media Full Time Junior-Mid</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Media Image</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://the-media-image.com/careers/paid-media-associate-argentina/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Graduate Programme: Paid Media Analyst (South Africa) SA Remote Paid Media Full Time Junior</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Media Image</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://the-media-image.com/careers/graduate-programme-paid-media-analyst/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Junior Data Scientist (United Kingdom) UK Hybrid Data Science &amp; Engineering Full Time Junior</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Media Image</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://the-media-image.com/careers/junior-data-scientist/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Paid Media Executive</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://upriseup.co.uk/careers/paid-media-executive/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Digital Media Data Assistant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://upriseup.co.uk/careers/digital-media-data-assistant/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Paid Digital Media Assistant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://upriseup.co.uk/careers/paid-digital-media-assistant/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Paid Digital Media Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://upriseup.co.uk/careers/paid-digital-media-analyst/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SEO Assistant</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://upriseup.co.uk/careers/seo-assistant/</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SEO Analyst</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://upriseup.co.uk/careers/seo-analyst/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>News 21 September, 2026 HM Land Registry drives forward data modernisation programme with Version 1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Version 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.version1.com/news/hm-land-registry-drives-forward-data-modernisation-programme-with-version-1/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Trainee Social Media Assistant</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Netcom Online Learning</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.reed.co.uk/jobs/trainee-social-media-assistant/57500395</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Trainee Social Media Executive</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Netcom Online Learning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.reed.co.uk/jobs/trainee-social-media-executive/57500406</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Trainee Social Media Specialist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Netcom Online Learning</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.reed.co.uk/jobs/trainee-social-media-specialist/57500398</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Part Time Marketing &amp; Design Executive</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Parkside Office Professional</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.reed.co.uk/jobs/part-time-marketing-design-executive/57479018</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Trainee Digital Marketing Executive</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ITOL Recruit</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.reed.co.uk/jobs/trainee-digital-marketing-executive/57482906</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Spanish and Japanese Sales Account Executive</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>People First</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.reed.co.uk/jobs/spanish-and-japanese-sales-account-executive/57480189</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Account Executive - SAAS / Enterprise - B2B - Global Fintech Sector..</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hawke Search </t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.reed.co.uk/jobs/account-executive-saas-enterprise-b2b-global-fintech-sector/57482672</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>New Business Account Executive – MSPS, Outsourced Service, Integration Services, Service Based SaaS.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Global Technology Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.reed.co.uk/jobs/new-business-account-executive--msps-outsourced-service-integration-services-service-based-saas/57487256</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Assistant, Digital Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fifth Season</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5940234757?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Agency New Business Executive (Digital Marketing)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5931112462?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Trading Performance Analyst - Hospitals &amp; Primary Care</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nuffield Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5936270512?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CIBSE Certification Marketing Executive</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cibse</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5940251788?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Social Media Executive - Training Course</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Netcom Training</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5938299681?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Freelance Social Media &amp; Marketing Executive</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>StudioXAG</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5939062483?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Interim Marketing Coordinator</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Frasers Hospitality</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5945045489?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Temporary Marketing Assistant</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Michael Page</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5936932882?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Trainee Sales &amp; Marketing Assistant</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Horizon</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5930698734?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Marketing Assistant - No Experience Required</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Growth for Good</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5934612226?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Account Executive, Media Sales</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Blis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5942325792?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>New Business Executive at United Media</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>United Media</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5937643216?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Marketing Executive (12M Fixed Term Contract)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Enra Specialist Finance</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5931443469?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PT Data Analysis &amp; Marketing/Sales Intern</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Bosch Group</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5936256509?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9627,7 +8237,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -9683,7 +8293,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>error: HTTPError: 404 Client Error: Not Found for url: https://crucible.io/working-at-crucible/</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -9847,7 +8457,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -10607,7 +9217,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -10667,7 +9277,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -11847,7 +10457,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -11867,7 +10477,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -11947,7 +10557,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -12007,7 +10617,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">

--- a/review-2026-10-30.xlsx
+++ b/review-2026-10-30.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>greenhouse:5439637008</t>
+          <t>greenhouse:5417679008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -748,7 +748,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5439637008</t>
+          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5417679008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1221,7 +1221,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>teamtailor:083ce943-e481-42c7-a1bf-4076a9e58b74</t>
+          <t>jibe:174678</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Digital Media Executive</t>
+          <t>Account Executive (Graduate/Entry) - Health</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AKA UK</t>
+          <t>Publicis Groupe - BBH</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>teamtailor</t>
+          <t>jibe</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://careers.akauk.com/jobs/8630703-digital-media-executive</t>
+          <t>https://careers.publicisgroupe.com/jobs/174678?lang=en-us</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>greenhouse:8882147002</t>
+          <t>jibe:174736</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1292,23 +1292,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UK Graduate Leadership Programme - Media Marketing Track (July Start)</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Digital Voices</t>
+          <t>Publicis Groupe - Taylor Herring</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>London, England, United Kingdom</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>jibe</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/pmg/jobs/8882147002</t>
+          <t>https://careers.publicisgroupe.com/jobs/174736?lang=en-us</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>careers-page:https://www.fdry.com/careers/digital-marketing-executive/</t>
+          <t>jibe:178354</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1348,17 +1348,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive</t>
+          <t>Analyst (Media)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FDRY</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>Publicis Groupe - Digitas UK</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1366,12 +1374,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>jibe</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.fdry.com/careers/digital-marketing-executive/</t>
+          <t>https://careers.publicisgroupe.com/jobs/178354?lang=en-us</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1381,7 +1389,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>careers-page:https://www.fdry.com/careers/account-executive/</t>
+          <t>jibe:178754</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1396,17 +1404,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Client Development Associate</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FDRY</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>Publicis Groupe - CJ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1414,12 +1430,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>jibe</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.fdry.com/careers/account-executive/</t>
+          <t>https://careers.publicisgroupe.com/jobs/178754?lang=en-us</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1429,7 +1445,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>careers-page:https://kaizen.co.uk/careers/digital-pr-assistant</t>
+          <t>jibe:175855</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1444,17 +1460,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Digital PR Assistant</t>
+          <t>Creative and Design Executive</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaizen</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>Publicis Groupe - Publicis Media</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1462,12 +1486,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>jibe</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://kaizen.co.uk/careers/digital-pr-assistant</t>
+          <t>https://careers.publicisgroupe.com/jobs/175855?lang=en-us</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1477,7 +1501,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>teamtailor:c6b3417c-a766-4e9f-a18e-a49d0d509e01</t>
+          <t>jibe:177357</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1492,12 +1516,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Associate Programmatic Trader</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>krow group</t>
+          <t>Publicis Groupe - Epsilon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1508,7 +1532,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1518,12 +1542,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>teamtailor</t>
+          <t>jibe</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://themissiongroup-bray-leino-agency.teamtailor.com/jobs/8583110-account-executive</t>
+          <t>https://careers.publicisgroupe.com/jobs/177357?lang=en-us</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1533,7 +1557,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>careers-page:https://www.tugagency.com/about-agency/careers/paid-media-account-executive/</t>
+          <t>jibe:175743</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1548,17 +1572,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paid Media Account Executive</t>
+          <t>Client Development Associate (Retail Media)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tug Agency</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>Publicis Groupe - Epsilon</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1566,12 +1598,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>jibe</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.tugagency.com/about-agency/careers/paid-media-account-executive/</t>
+          <t>https://careers.publicisgroupe.com/jobs/175743?lang=en-us</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1581,7 +1613,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>careers-page:https://unity.online/careers/marketing-executive/</t>
+          <t>teamtailor:083ce943-e481-42c7-a1bf-4076a9e58b74</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1596,17 +1628,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Marketing Executive</t>
+          <t>Digital Media Executive</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Unity Online</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>AKA UK</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1614,12 +1654,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>careers-page</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://unity.online/careers/marketing-executive/</t>
+          <t>https://careers.akauk.com/jobs/8630703-digital-media-executive</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1629,7 +1669,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>teamtailor:b12cf74c-3316-4a42-8bb8-044bf6f23c17</t>
+          <t>greenhouse:8882147002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1644,23 +1684,23 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Junior Paid Media Consultant</t>
+          <t>UK Graduate Leadership Programme - Media Marketing Track (July Start)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vervaunt</t>
+          <t>Digital Voices</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>London, England, United Kingdom</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1670,12 +1710,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>teamtailor</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://team.vervaunt.com/jobs/8464967-junior-paid-media-consultant</t>
+          <t>https://job-boards.greenhouse.io/pmg/jobs/8882147002</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1685,7 +1725,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>careers-page:https://wma.agency/careers/marketing-social-media-internship-ny/</t>
+          <t>careers-page:https://www.fdry.com/careers/digital-marketing-executive/</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1700,12 +1740,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Marketing &amp; Social Media Internship</t>
+          <t>Digital Marketing Executive</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WMA</t>
+          <t>FDRY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1723,7 +1763,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://wma.agency/careers/marketing-social-media-internship-ny/</t>
+          <t>https://www.fdry.com/careers/digital-marketing-executive/</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1733,7 +1773,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>reed:57497958</t>
+          <t>careers-page:https://www.fdry.com/careers/account-executive/</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1748,29 +1788,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Marketing Content Assistant</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Handle Recruitment</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>£30,000–£35,000</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+          <t>FDRY</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1778,12 +1806,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/marketing-content-assistant/57497958</t>
+          <t>https://www.fdry.com/careers/account-executive/</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1793,7 +1821,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>reed:57497867</t>
+          <t>careers-page:https://kaizen.co.uk/careers/digital-pr-assistant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1808,29 +1836,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Content Assistant</t>
+          <t>Digital PR Assistant</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Michael Page Business Support</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Guildford</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>£28,000–£32,000</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+          <t>Kaizen</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1838,12 +1854,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/content-assistant/57497867</t>
+          <t>https://kaizen.co.uk/careers/digital-pr-assistant</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1853,7 +1869,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>reed:57502657</t>
+          <t>teamtailor:c6b3417c-a766-4e9f-a18e-a49d0d509e01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1868,12 +1884,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Michael Page Digital</t>
+          <t>krow group</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1884,7 +1900,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1894,12 +1910,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/digital-marketing-executive/57502657</t>
+          <t>https://themissiongroup-bray-leino-agency.teamtailor.com/jobs/8583110-account-executive</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1909,7 +1925,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>reed:57473930</t>
+          <t>careers-page:https://www.tugagency.com/about-agency/careers/paid-media-account-executive/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1924,29 +1940,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Marketing Campaign Executive</t>
+          <t>Paid Media Account Executive</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The Portfolio Group</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>£32,000–£38,000</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>Tug Agency</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -1954,12 +1958,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/marketing-campaign-executive/57473930</t>
+          <t>https://www.tugagency.com/about-agency/careers/paid-media-account-executive/</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1969,7 +1973,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>reed:57475904</t>
+          <t>careers-page:https://unity.online/careers/marketing-executive/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1984,29 +1988,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Performance Marketing Executive</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Handle Recruitment</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>£30,000–£35,000</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
+          <t>Unity Online</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2014,12 +2006,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/performance-marketing-executive/57475904</t>
+          <t>https://unity.online/careers/marketing-executive/</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2029,7 +2021,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>reed:57503820</t>
+          <t>careers-page:https://upriseup.co.uk/careers/paid-media-executive/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2044,29 +2036,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Social Media Executive</t>
+          <t>Paid Media Executive</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sphere Digital Recruitment</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>£33,000–£37,000</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2074,12 +2054,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/social-media-executive/57503820</t>
+          <t>https://upriseup.co.uk/careers/paid-media-executive/</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2089,7 +2069,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>reed:57478149</t>
+          <t>careers-page:https://upriseup.co.uk/careers/digital-media-data-assistant/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2104,29 +2084,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Shopper Marketing Executive</t>
+          <t>Digital Media Data Assistant</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pursuit Resources Group</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>£32,000–£35,000</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2134,12 +2102,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/shopper-marketing-executive/57478149</t>
+          <t>https://upriseup.co.uk/careers/digital-media-data-assistant/</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2149,7 +2117,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>reed:57498820</t>
+          <t>careers-page:https://upriseup.co.uk/careers/paid-digital-media-assistant/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2164,25 +2132,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>E-Commerce Executive</t>
+          <t>Paid Digital Media Assistant</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pursuit Resources Group</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2190,12 +2150,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/e-commerce-executive/57498820</t>
+          <t>https://upriseup.co.uk/careers/paid-digital-media-assistant/</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2205,7 +2165,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>reed:57500761</t>
+          <t>careers-page:https://upriseup.co.uk/careers/paid-digital-media-analyst/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2220,29 +2180,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Amazon Marketplace and PPC Executive</t>
+          <t>Paid Digital Media Analyst</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Get Staffed Online Recruitment Limited</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>£44,000–£47,000</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2250,12 +2198,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/amazon-marketplace-and-ppc-executive/57500761</t>
+          <t>https://upriseup.co.uk/careers/paid-digital-media-analyst/</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2265,7 +2213,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>reed:57467709</t>
+          <t>careers-page:https://upriseup.co.uk/careers/seo-assistant/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2280,29 +2228,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Account Executive - Media - Hybrid</t>
+          <t>SEO Assistant</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aaron Wallis Sales Recruitment</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>West London</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>£35,000</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2310,12 +2246,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/account-executive-media-hybrid/57467709</t>
+          <t>https://upriseup.co.uk/careers/seo-assistant/</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2325,7 +2261,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>reed:57487106</t>
+          <t>careers-page:https://upriseup.co.uk/careers/seo-analyst/</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2340,29 +2276,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PR and Communications Executive</t>
+          <t>SEO Analyst</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The Law Support Group</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>£40,000–£45,000</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
+          <t>Uprise Up</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2370,12 +2294,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/pr-and-communications-executive/57487106</t>
+          <t>https://upriseup.co.uk/careers/seo-analyst/</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,7 +2309,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>reed:57476858</t>
+          <t>teamtailor:b12cf74c-3316-4a42-8bb8-044bf6f23c17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2400,12 +2324,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Graduate Marketing (CSA)</t>
+          <t>Junior Paid Media Consultant</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sphere Digital Recruitment</t>
+          <t>Vervaunt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2413,14 +2337,10 @@
           <t>London</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>£38,000</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2430,12 +2350,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.reed.co.uk/jobs/graduate-marketing-csa/57476858</t>
+          <t>https://team.vervaunt.com/jobs/8464967-junior-paid-media-consultant</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2445,7 +2365,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adzuna:5934431056</t>
+          <t>careers-page:https://wma.agency/careers/marketing-social-media-internship-ny/</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2460,25 +2380,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Marketing and Digital Assistant</t>
+          <t>Marketing &amp; Social Media Internship</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Handle Recruitment</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>South West London, London</t>
-        </is>
-      </c>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2026-10-30</t>
@@ -2486,12 +2398,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>careers-page</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5934431056?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://wma.agency/careers/marketing-social-media-internship-ny/</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2501,7 +2413,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adzuna:5939916419</t>
+          <t>reed:57497958</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2516,27 +2428,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Italian Digital PR Assistant</t>
+          <t>Marketing Content Assistant</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>The Opportunity Hub UK</t>
+          <t>Handle Recruitment</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>£28,000–£30,000</t>
+          <t>£30,000–£35,000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2546,12 +2458,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5939916419?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/marketing-content-assistant/57497958</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2561,7 +2473,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adzuna:5936755442</t>
+          <t>reed:57497867</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2576,27 +2488,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Marketing Assistant</t>
+          <t>Content Assistant</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Taylor James Resourcing Limited</t>
+          <t>Michael Page Business Support</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>East London, London</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£28,000–£32,000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2606,12 +2518,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936755442?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/content-assistant/57497867</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2621,7 +2533,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adzuna:5940270542</t>
+          <t>reed:57502657</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2641,18 +2553,18 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ocuco</t>
+          <t>Michael Page Digital</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gunnersbury, West London</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2662,12 +2574,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940270542?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/digital-marketing-executive/57502657</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2677,7 +2589,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adzuna:5945254837</t>
+          <t>reed:57473930</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2692,23 +2604,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive</t>
+          <t>Marketing Campaign Executive</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walr</t>
+          <t>The Portfolio Group</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>North Lambeth, South East London</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>£32,000–£38,000</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2718,12 +2634,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945254837?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/marketing-campaign-executive/57473930</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2733,7 +2649,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adzuna:5938546986</t>
+          <t>reed:57475904</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2748,23 +2664,27 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive, UK Digital Acquisition</t>
+          <t>Performance Marketing Executive</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Handle Recruitment</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>£30,000–£35,000</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2774,12 +2694,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546986?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/performance-marketing-executive/57475904</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2789,7 +2709,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adzuna:5937070665</t>
+          <t>reed:57503820</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2804,23 +2724,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Digital Marketing &amp; Content Executive</t>
+          <t>Social Media Executive</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Dorchester</t>
+          <t>Sphere Digital Recruitment</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>£33,000–£37,000</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2830,12 +2754,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937070665?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/social-media-executive/57503820</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2845,7 +2769,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>adzuna:5945448806</t>
+          <t>reed:57478149</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2860,27 +2784,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Digital Marketing &amp; Content Executive</t>
+          <t>Shopper Marketing Executive</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dorchester Collection</t>
+          <t>Pursuit Resources Group</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mayfair, West London</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>£12,000</t>
+          <t>£32,000–£35,000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2890,12 +2814,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945448806?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/shopper-marketing-executive/57478149</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2905,7 +2829,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>adzuna:5935181643</t>
+          <t>reed:57498820</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2920,27 +2844,23 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Digital Marketing Analyst</t>
+          <t>E-Commerce Executive</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>The Opportunity Hub UK</t>
+          <t>Pursuit Resources Group</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>£25,000–£30,000</t>
-        </is>
-      </c>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2950,12 +2870,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5935181643?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/e-commerce-executive/57498820</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2965,7 +2885,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>adzuna:5936350462</t>
+          <t>reed:57500761</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2980,23 +2900,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Marketing Executive - Entertainment &amp; Live Experiences</t>
+          <t>Amazon Marketplace and PPC Executive</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>The Event Academy</t>
+          <t>Get Staffed Online Recruitment Limited</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>£44,000–£47,000</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3006,12 +2930,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936350462?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/amazon-marketplace-and-ppc-executive/57500761</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3021,7 +2945,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>adzuna:5943783539</t>
+          <t>reed:57467709</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3036,23 +2960,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Content Marketing Executive</t>
+          <t>Account Executive - Media - Hybrid</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Grundon</t>
+          <t>Aaron Wallis Sales Recruitment</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Slough, Berkshire</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>West London</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>£35,000</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3062,12 +2990,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943783539?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/account-executive-media-hybrid/57467709</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3077,7 +3005,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>adzuna:5940234751</t>
+          <t>reed:57487106</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3092,23 +3020,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Marketing Executive</t>
+          <t>PR and Communications Executive</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Veriforce</t>
+          <t>The Law Support Group</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>£40,000–£45,000</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3118,12 +3050,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940234751?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/pr-and-communications-executive/57487106</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3133,7 +3065,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>adzuna:5943403879</t>
+          <t>reed:57476858</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3148,23 +3080,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Graduate Marketing (CSA)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MarketFully</t>
+          <t>Sphere Digital Recruitment</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>£38,000</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3174,12 +3110,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>reed</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943403879?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.reed.co.uk/jobs/graduate-marketing-csa/57476858</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3189,7 +3125,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>adzuna:5943655740</t>
+          <t>adzuna:5934431056</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3204,27 +3140,23 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Social Media Executive</t>
+          <t>Marketing and Digital Assistant</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mumsnet</t>
+          <t>Handle Recruitment</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kentish Town, North West London</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>£32,000–£35,000</t>
-        </is>
-      </c>
+          <t>South West London, London</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3239,7 +3171,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943655740?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5934431056?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3249,7 +3181,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>adzuna:5930230212</t>
+          <t>adzuna:5939916419</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3264,12 +3196,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Global Social Media Executive</t>
+          <t>Italian Digital PR Assistant</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Collinson</t>
+          <t>The Opportunity Hub UK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3277,10 +3209,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>£28,000–£30,000</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3295,7 +3231,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930230212?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5939916419?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3305,7 +3241,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>adzuna:5945456204</t>
+          <t>adzuna:5936755442</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3320,27 +3256,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Social Media and Content Executive</t>
+          <t>Marketing Assistant</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dorchester Collection</t>
+          <t>Taylor James Resourcing Limited</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mayfair, West London</t>
+          <t>East London, London</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>£12,000</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3355,7 +3291,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945456204?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936755442?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3365,7 +3301,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>adzuna:5944487008</t>
+          <t>adzuna:5940270542</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3380,27 +3316,23 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Social Media &amp; Creative Content Executive</t>
+          <t>Digital Marketing Executive</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>The Hari</t>
+          <t>Ocuco</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knightsbridge, South West London</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>£28,840</t>
-        </is>
-      </c>
+          <t>Gunnersbury, West London</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3415,7 +3347,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944487008?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940270542?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3425,7 +3357,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>adzuna:5936724448</t>
+          <t>adzuna:5945254837</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3440,27 +3372,23 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Brand Development Executive</t>
+          <t>Digital Marketing Executive</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Universal Business Team</t>
+          <t>Walr</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sidcup, Kent</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>£35,000–£40,000</t>
-        </is>
-      </c>
+          <t>North Lambeth, South East London</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3475,7 +3403,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936724448?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945254837?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3485,7 +3413,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>adzuna:5934293105</t>
+          <t>adzuna:5938546986</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3500,12 +3428,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Social Media Assistant</t>
+          <t>Digital Marketing Executive, UK Digital Acquisition</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Reed</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3513,14 +3441,10 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>£26,436</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3535,7 +3459,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5934293105?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546986?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3545,7 +3469,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>adzuna:5945446464</t>
+          <t>adzuna:5937070665</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3560,23 +3484,23 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Social Media Assistant (UK)</t>
+          <t>Digital Marketing &amp; Content Executive</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>The Dorchester</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chiswick, West London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3591,7 +3515,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945446464?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937070665?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3601,7 +3525,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>adzuna:5937652834</t>
+          <t>adzuna:5945448806</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3616,23 +3540,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Social Media &amp; Community Management Assistant</t>
+          <t>Digital Marketing &amp; Content Executive</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nationwide</t>
+          <t>Dorchester Collection</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liverpool Street, Central London</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Mayfair, West London</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>£12,000</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3647,7 +3575,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937652834?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945448806?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3657,7 +3585,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>adzuna:5938546255</t>
+          <t>adzuna:5935181643</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3672,12 +3600,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Social Video Intern</t>
+          <t>Digital Marketing Analyst</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>The Opportunity Hub UK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3685,10 +3613,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>£25,000–£30,000</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3703,7 +3635,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546255?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5935181643?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3713,7 +3645,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>adzuna:5938546249</t>
+          <t>adzuna:5936350462</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3728,12 +3660,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Communications Intern (Universal Destinations &amp; Experiences)</t>
+          <t>Marketing Executive - Entertainment &amp; Live Experiences</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>The Event Academy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3744,7 +3676,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3759,7 +3691,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546249?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936350462?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3769,7 +3701,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>adzuna:5944766327</t>
+          <t>adzuna:5943783539</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3784,23 +3716,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Marketing Assistant</t>
+          <t>Content Marketing Executive</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Grundon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Slough, Berkshire</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3815,7 +3747,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944766327?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943783539?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3825,7 +3757,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>adzuna:5944934685</t>
+          <t>adzuna:5940234751</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3840,23 +3772,23 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Performance Marketing Assistant</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Charles Tyrwhitt</t>
+          <t>Veriforce</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>The City, Central London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3871,7 +3803,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944934685?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940234751?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3881,7 +3813,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>adzuna:5937647997</t>
+          <t>adzuna:5943403879</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3896,23 +3828,23 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Talent &amp; Marketing Assistant</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hansen Filler Associates Limited</t>
+          <t>MarketFully</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Farringdon, Central London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3927,7 +3859,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/land/ad/5937647997?se=mqPtf0bU8RGBsqu62qDD-w&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=9057C89125C435ECC44218FCA93AEB0B306255F5</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943403879?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3937,7 +3869,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>adzuna:5937651662</t>
+          <t>adzuna:5943655740</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3952,23 +3884,27 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Marketing Assistant EMEA - Shaw Contract</t>
+          <t>Social Media Executive</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>Mumsnet</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Farringdon, Central London</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Kentish Town, North West London</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>£32,000–£35,000</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3983,7 +3919,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937651662?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943655740?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3993,7 +3929,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>adzuna:5937237472</t>
+          <t>adzuna:5930230212</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4008,12 +3944,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Marketing Assistant EMEA - Shaw Contract</t>
+          <t>Global Social Media Executive</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shaw Industries Inc</t>
+          <t>Collinson</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4024,7 +3960,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4039,7 +3975,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937237472?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5930230212?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4049,7 +3985,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>adzuna:5935270588</t>
+          <t>adzuna:5945456204</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4064,23 +4000,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Email Marketing Operations Assistant</t>
+          <t>Social Media and Content Executive</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Decentralized Masters</t>
+          <t>Dorchester Collection</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Mayfair, West London</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>£12,000</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4095,7 +4035,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5935270588?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945456204?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4105,7 +4045,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>adzuna:5945753704</t>
+          <t>adzuna:5944487008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4120,27 +4060,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Marketing and Communications Assistant</t>
+          <t>Social Media &amp; Creative Content Executive</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Start People Ltd</t>
+          <t>The Hari</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hounslow, London</t>
+          <t>Knightsbridge, South West London</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>£34,000–£37,000</t>
+          <t>£28,840</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4155,7 +4095,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945753704?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944487008?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4165,7 +4105,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>adzuna:5932702272</t>
+          <t>adzuna:5936724448</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4180,23 +4120,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Marketing Intern - Rimmel</t>
+          <t>Brand Development Executive</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Coty</t>
+          <t>Universal Business Team</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>Sidcup, Kent</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>£35,000–£40,000</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4211,7 +4155,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5932702272?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936724448?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4221,7 +4165,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>adzuna:5940948225</t>
+          <t>adzuna:5934293105</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4236,12 +4180,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Social Media Assistant</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Coty</t>
+          <t>Reed</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4249,10 +4193,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>£26,436</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4267,7 +4215,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940948225?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5934293105?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4277,7 +4225,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>adzuna:5942771268</t>
+          <t>adzuna:5945446464</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4292,27 +4240,23 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Travel Product and Marketing Executive</t>
+          <t>Social Media Assistant (UK)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Antella Travel Recruitment</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aldwych, Central London</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>£34,000–£40,000</t>
-        </is>
-      </c>
+          <t>Chiswick, West London</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4327,7 +4271,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5942771268?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945446464?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4337,7 +4281,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>adzuna:5938360400</t>
+          <t>adzuna:5937652834</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4352,24 +4296,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SEO Executive</t>
+          <t>Social Media &amp; Community Management Assistant</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Additional Resources</t>
+          <t>Nationwide</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Leavesden, Watford</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>£30,000–£35,000</t>
-        </is>
-      </c>
+          <t>Liverpool Street, Central London</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4387,7 +4327,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938360400?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937652834?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4397,7 +4337,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>adzuna:5936933181</t>
+          <t>adzuna:5938546255</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4412,27 +4352,23 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Content / SEO Assistant</t>
+          <t>Social Video Intern</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mandeville</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Farringdon, Central London</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>£32,000–£36,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4447,7 +4383,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936933181?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546255?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4457,7 +4393,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>adzuna:5944530723</t>
+          <t>adzuna:5938546249</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4472,12 +4408,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Amazon Marketplace and PPC Executive</t>
+          <t>Communications Intern (Universal Destinations &amp; Experiences)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AC Global</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4485,14 +4421,10 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>£44,000–£47,000</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4507,7 +4439,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944530723?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546249?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4517,7 +4449,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>adzuna:5940250032</t>
+          <t>adzuna:5944766327</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4532,23 +4464,23 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Display &amp; Paid Social executive</t>
+          <t>Marketing Assistant</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IG Group</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>The City, Central London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4563,7 +4495,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940250032?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944766327?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4573,7 +4505,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>adzuna:5931858760</t>
+          <t>adzuna:5944934685</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4588,23 +4520,23 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Biddable Executive (Paid Social &amp; Programmatic)</t>
+          <t>Performance Marketing Assistant</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Havas</t>
+          <t>Charles Tyrwhitt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>The City, Central London</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4619,7 +4551,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931858760?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944934685?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4629,7 +4561,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>adzuna:5936453313</t>
+          <t>adzuna:5937647997</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4644,23 +4576,23 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paid Media Executive</t>
+          <t>Talent &amp; Marketing Assistant</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Topdeck Travel</t>
+          <t>Hansen Filler Associates Limited</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gunnersbury, West London</t>
+          <t>Farringdon, Central London</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4675,7 +4607,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936453313?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/land/ad/5937647997?se=4kntglDU8RGRHZ-5SzG_oA&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=9057C89125C435ECC44218FCA93AEB0B306255F5</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4685,7 +4617,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>adzuna:5944924185</t>
+          <t>adzuna:5937651662</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4700,27 +4632,23 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Graduate Media Account Executive</t>
+          <t>Marketing Assistant EMEA - Shaw Contract</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BrighterBox</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>£26,000</t>
-        </is>
-      </c>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4735,7 +4663,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944924185?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937651662?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4745,7 +4673,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>adzuna:5938296013</t>
+          <t>adzuna:5937237472</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4760,12 +4688,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Regional Digital Media &amp; Content Executive – UK &amp; EU</t>
+          <t>Marketing Assistant EMEA - Shaw Contract</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>Shaw Industries Inc</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4773,11 +4701,7 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>£36,837</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4795,7 +4719,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938296013?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937237472?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4805,7 +4729,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>adzuna:5944336335</t>
+          <t>adzuna:5935270588</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4820,12 +4744,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Growth Marketing Executive</t>
+          <t>Email Marketing Operations Assistant</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Treatwell</t>
+          <t>Decentralized Masters</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4833,14 +4757,10 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>£42,000</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4855,7 +4775,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944336335?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5935270588?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4865,7 +4785,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>adzuna:5946683887</t>
+          <t>adzuna:5945753704</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4880,23 +4800,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PR &amp; Communications Executive</t>
+          <t>Marketing and Communications Assistant</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Collinson</t>
+          <t>Start People Ltd</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>Hounslow, London</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>£34,000–£37,000</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4911,7 +4835,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5946683887?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945753704?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4921,7 +4845,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>adzuna:5945458765</t>
+          <t>adzuna:5932702272</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4936,12 +4860,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Account Executive, Influencer Marketing</t>
+          <t>Marketing Intern - Rimmel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Acceleration Partners</t>
+          <t>Coty</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4949,14 +4873,10 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>£27,000–£37,000</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4971,7 +4891,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945458765?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5932702272?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4981,7 +4901,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>adzuna:5934032852</t>
+          <t>adzuna:5940948225</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4996,12 +4916,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Strategic Account Executive</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pilot Thomas Logistics</t>
+          <t>Coty</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5012,7 +4932,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5027,7 +4947,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5934032852?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940948225?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -5037,7 +4957,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>adzuna:5944530692</t>
+          <t>adzuna:5942771268</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5052,27 +4972,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Content Executive</t>
+          <t>Travel Product and Marketing Executive</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Auxo Future Build</t>
+          <t>Antella Travel Recruitment</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Finchley, North London</t>
+          <t>Aldwych, Central London</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>£26,500–£27,000</t>
+          <t>£34,000–£40,000</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5087,7 +5007,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944530692?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5942771268?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5097,7 +5017,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>adzuna:5938546221</t>
+          <t>adzuna:5938360400</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5112,23 +5032,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Acquired Content Distribution Strategy Intern</t>
+          <t>SEO Executive</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>Additional Resources</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>Leavesden, Watford</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>£30,000–£35,000</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5143,7 +5067,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546221?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938360400?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5153,7 +5077,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>adzuna:5938546260</t>
+          <t>adzuna:5936933181</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5168,23 +5092,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Corporate Communications Intern</t>
+          <t>Content / SEO Assistant</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>Mandeville</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>£32,000–£36,000</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5199,7 +5127,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546260?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936933181?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5209,7 +5137,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>adzuna:5939000242</t>
+          <t>adzuna:5944530723</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5224,12 +5152,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Business Marketing Operations Associate - Publishing</t>
+          <t>Amazon Marketplace and PPC Executive</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>AC Global</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5237,10 +5165,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>£44,000–£47,000</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5255,7 +5187,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/land/ad/5939000242?se=8gxJgUbU8RGQ-s1xb079dA&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=E765009762CC63ACAF94DF3F47D207C928022DA1</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944530723?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5265,7 +5197,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>adzuna:5937111775</t>
+          <t>adzuna:5940250032</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5280,27 +5212,23 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Digital Coordinator</t>
+          <t>Display &amp; Paid Social executive</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Office Angels</t>
+          <t>IG Group</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Covent Garden, Central London</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>£29,000–£31,000</t>
-        </is>
-      </c>
+          <t>The City, Central London</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5315,7 +5243,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937111775?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5940250032?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5325,7 +5253,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>adzuna:5939062485</t>
+          <t>adzuna:5931858760</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5340,12 +5268,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Content Executive</t>
+          <t>Biddable Executive (Paid Social &amp; Programmatic)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>re:act marketing ltd</t>
+          <t>Havas</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5356,7 +5284,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5371,7 +5299,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5939062485?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5931858760?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5381,7 +5309,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>adzuna:5944670547</t>
+          <t>adzuna:5936453313</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5396,23 +5324,23 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Community Executive</t>
+          <t>Paid Media Executive</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Founders Forum Group</t>
+          <t>Topdeck Travel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Gunnersbury, West London</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5427,7 +5355,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944670547?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5936453313?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5437,7 +5365,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>adzuna:5938546239</t>
+          <t>adzuna:5944924185</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5452,12 +5380,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Audience Insights &amp; Analytics Intern</t>
+          <t>Graduate Media Account Executive</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>BrighterBox</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5465,10 +5393,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>£26,000</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5483,7 +5415,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546239?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944924185?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5493,7 +5425,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>adzuna:5935226000</t>
+          <t>adzuna:5938296013</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5508,12 +5440,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Social Media Coordinator</t>
+          <t>Regional Digital Media &amp; Content Executive – UK &amp; EU</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dr. Martens</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5521,10 +5453,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>£36,837</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5539,7 +5475,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5935226000?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938296013?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5549,7 +5485,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>adzuna:5931392610</t>
+          <t>adzuna:5944336335</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5564,23 +5500,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Communications Associate - SAP UK Intern (13 Month Placement)</t>
+          <t>Growth Marketing Executive</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Treatwell</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Feltham, London</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>£42,000</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5595,7 +5535,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931392610?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944336335?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5605,7 +5545,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>adzuna:5938546236</t>
+          <t>adzuna:5946683887</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5620,12 +5560,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Content Planning &amp; Acquisitions Intern</t>
+          <t>PR &amp; Communications Executive</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>Collinson</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5636,7 +5576,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5651,7 +5591,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546236?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5946683887?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5661,7 +5601,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>adzuna:5946686259</t>
+          <t>adzuna:5945458765</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5676,12 +5616,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>UK Graduate Leadership Programme - Media Marketing Track (July Start)</t>
+          <t>Account Executive, Influencer Marketing</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PMG</t>
+          <t>Acceleration Partners</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5689,10 +5629,14 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>£27,000–£37,000</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5707,7 +5651,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5946686259?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5945458765?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5717,7 +5661,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>adzuna:5930241938</t>
+          <t>adzuna:5934032852</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5732,12 +5676,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Strategic Account Executive</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stelia</t>
+          <t>Pilot Thomas Logistics</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5745,14 +5689,10 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>£28,000</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5767,7 +5707,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930241938?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5934032852?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5777,7 +5717,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>adzuna:5943453576</t>
+          <t>adzuna:5944530692</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5792,23 +5732,27 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Marketing Apprentice</t>
+          <t>Content Executive</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Auxo Future Build</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
+          <t>Finchley, North London</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>£26,500–£27,000</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5823,7 +5767,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943453576?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944530692?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5833,7 +5777,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>adzuna:5930276586</t>
+          <t>adzuna:5938546221</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5848,12 +5792,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Lifecycle Marketing Intern</t>
+          <t>Acquired Content Distribution Strategy Intern</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Teya</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5864,7 +5808,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5879,7 +5823,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930276586?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546221?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5889,7 +5833,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>adzuna:5938546231</t>
+          <t>adzuna:5938546260</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5904,7 +5848,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Trade Marketing Intern</t>
+          <t>Corporate Communications Intern</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5935,7 +5879,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546231?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546260?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5945,7 +5889,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>adzuna:5940073573</t>
+          <t>adzuna:5939000242</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5960,23 +5904,23 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AI &amp; Digital Marketing Apprentice</t>
+          <t>Business Marketing Operations Associate - Publishing</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hollywood Bowl Group</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hemel Hempstead, Hertfordshire</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5991,7 +5935,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940073573?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/land/ad/5939000242?se=aLYbhVDU8RGRHZ-5SzG_oA&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=E765009762CC63ACAF94DF3F47D207C928022DA1</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -6001,7 +5945,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>adzuna:5931144491</t>
+          <t>adzuna:5937111775</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6016,23 +5960,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>BBM UK Marketing Intern</t>
+          <t>Digital Coordinator</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bosch Group</t>
+          <t>Office Angels</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Denham, Buckinghamshire</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>Covent Garden, Central London</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>£29,000–£31,000</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6047,7 +5995,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931144491?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5937111775?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -6057,7 +6005,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>adzuna:5938546235</t>
+          <t>adzuna:5939062485</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6072,12 +6020,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Franchise Marketing Intern (Consumer Products)</t>
+          <t>Content Executive</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>NBC Universal</t>
+          <t>re:act marketing ltd</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6103,7 +6051,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938546235?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5939062485?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6113,7 +6061,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>adzuna:5945463670</t>
+          <t>adzuna:5944670547</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6128,12 +6076,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Intern, Brand Marketing &amp; Media EMEAI</t>
+          <t>Community Executive</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tapestry</t>
+          <t>Founders Forum Group</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6144,7 +6092,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6159,7 +6107,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945463670?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5944670547?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6169,7 +6117,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>adzuna:5944311957</t>
+          <t>adzuna:5938546239</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6184,12 +6132,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Spring 2027 - Intern, Brand Marketing (London)</t>
+          <t>Audience Insights &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6200,7 +6148,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6215,7 +6163,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5944311957?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546239?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6225,7 +6173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>adzuna:5929514476</t>
+          <t>adzuna:5935226000</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6240,23 +6188,23 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Marketing Associate - SAP UK Intern (13 Month Placement)</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SAP IT Business Systeme</t>
+          <t>Dr. Martens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Feltham, London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6271,7 +6219,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5929514476?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5935226000?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6281,7 +6229,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>adzuna:5931392619</t>
+          <t>adzuna:5931392610</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6296,7 +6244,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Marketing Associate - SAP UK Intern (13 Month Placement)</t>
+          <t>Communications Associate - SAP UK Intern (13 Month Placement)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6327,7 +6275,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931392619?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5931392610?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6337,7 +6285,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>adzuna:5940948234</t>
+          <t>adzuna:5938546236</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6352,12 +6300,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PR and Communications Intern</t>
+          <t>Content Planning &amp; Acquisitions Intern</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Coty</t>
+          <t>NBC Universal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6368,7 +6316,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6383,7 +6331,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940948234?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546236?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6393,7 +6341,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>adzuna:5943784221</t>
+          <t>adzuna:5946686259</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6408,27 +6356,23 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Marketing Executive</t>
+          <t>UK Graduate Leadership Programme - Media Marketing Track (July Start)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Morson Edge</t>
+          <t>PMG</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>South West London, London</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>£30,000</t>
-        </is>
-      </c>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6443,7 +6387,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5943784221?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5946686259?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6453,7 +6397,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>adzuna:5940221334</t>
+          <t>adzuna:5930241938</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6468,23 +6412,27 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>PR Intern</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Glassworks London</t>
+          <t>Stelia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Haggerston, East London</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>£28,000</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6499,7 +6447,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/land/ad/5940221334?se=QC6xgUbU8RG_r4bmUg0vXw&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=2A631FA1C5085882063025A857E0FF695C7F8AC1</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5930241938?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6509,7 +6457,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>adzuna:5946684470</t>
+          <t>adzuna:5943453576</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6524,12 +6472,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Marketing &amp; Events Coordinator</t>
+          <t>Marketing Apprentice</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6537,14 +6485,10 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>£44,000–£55,000</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6559,7 +6503,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5946684470?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5943453576?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6569,7 +6513,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>adzuna:5930951195</t>
+          <t>adzuna:5930276586</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6584,17 +6528,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Marketing Executive</t>
+          <t>Lifecycle Marketing Intern</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>V-Nova</t>
+          <t>Teya</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paddington, West London</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -6615,12 +6559,748 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930951195?utm_medium=api&amp;utm_source=50c0f0cd</t>
+          <t>https://www.adzuna.co.uk/jobs/details/5930276586?utm_medium=api&amp;utm_source=50c0f0cd</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>adzuna:5938546231</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Trade Marketing Intern</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>NBC Universal</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546231?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>adzuna:5940073573</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AI &amp; Digital Marketing Apprentice</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Hollywood Bowl Group</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Hemel Hempstead, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5940073573?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>adzuna:5931144491</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>BBM UK Marketing Intern</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Bosch Group</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Denham, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5931144491?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>adzuna:5938546235</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Franchise Marketing Intern (Consumer Products)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>NBC Universal</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5938546235?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>adzuna:5945463670</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Intern, Brand Marketing &amp; Media EMEAI</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Tapestry</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5945463670?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>adzuna:5944311957</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Spring 2027 - Intern, Brand Marketing (London)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Excel Sports Management</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5944311957?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>adzuna:5929514476</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Marketing Associate - SAP UK Intern (13 Month Placement)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>SAP IT Business Systeme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Feltham, London</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5929514476?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>adzuna:5931392619</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Marketing Associate - SAP UK Intern (13 Month Placement)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Feltham, London</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5931392619?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>adzuna:5940948234</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PR and Communications Intern</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Coty</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5940948234?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>adzuna:5943784221</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Marketing Executive</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Morson Edge</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>South West London, London</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>£30,000</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5943784221?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>adzuna:5940221334</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>PR Intern</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Glassworks London</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Haggerston, East London</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/land/ad/5940221334?se=GH6ohVDU8RGRHZ-5SzG_oA&amp;utm_medium=api&amp;utm_source=50c0f0cd&amp;v=2A631FA1C5085882063025A857E0FF695C7F8AC1</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>adzuna:5946684470</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Events Coordinator</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Handshake</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>£44,000–£55,000</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5946684470?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>adzuna:5930951195</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>London &amp; around</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Marketing Executive</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>V-Nova</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Paddington, West London</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5930951195?utm_medium=api&amp;utm_source=50c0f0cd</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6633,7 +7313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6661,944 +7341,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Account Executive jobs 71,457 open jobs</t>
+          <t>Campaign Executive</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bountiful Cow</t>
+          <t>WPP Media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest-browse_jobs</t>
+          <t>https://job-boards.greenhouse.io/wppmedia/jobs/5439637008</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Production Coordinator jobs 20,645 open jobs</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/production-coordinator-jobs?trk=organization_guest-browse_jobs</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Account Executive jobs</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/account-executive-jobs?trk=organization_guest_linkster_link</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Marketing Assistant jobs</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/marketing-assistant-jobs?trk=organization_guest_linkster_link</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Marketing Intern jobs</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/marketing-intern-jobs?trk=organization_guest_linkster_link</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Public Relations Account Executive jobs</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/public-relations-account-executive-jobs?trk=organization_guest_linkster_link</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Assistant Producer jobs</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/assistant-producer-jobs?trk=organization_guest_linkster_link</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Client Executive jobs</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bountiful Cow</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/client-executive-jobs?trk=organization_guest_linkster_link</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Assistant Content Editor (News)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Reach Solutions</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://jobs.reachplc.com/job-description/id/744000157759180</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PPC Account Executive Cape Town Full Time Paid Media View role</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TIPi Group</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://weareroast.com/careers/ppc-account-executive-2/</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Graduate Program: Paid Media Analyst (Argentina) Argentina Remote Paid Media Full Time Junior</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>The Media Image</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://the-media-image.com/careers/graduate-program-paid-media-analyst-argentina/</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Paid Media Associate (Argentina) Argentina Remote Paid Media Full Time Junior-Mid</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>The Media Image</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://the-media-image.com/careers/paid-media-associate-argentina/</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Graduate Programme: Paid Media Analyst (South Africa) SA Remote Paid Media Full Time Junior</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The Media Image</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://the-media-image.com/careers/graduate-programme-paid-media-analyst/</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Junior Data Scientist (United Kingdom) UK Hybrid Data Science &amp; Engineering Full Time Junior</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>The Media Image</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://the-media-image.com/careers/junior-data-scientist/</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Paid Media Executive</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://upriseup.co.uk/careers/paid-media-executive/</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Digital Media Data Assistant</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://upriseup.co.uk/careers/digital-media-data-assistant/</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Paid Digital Media Assistant</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://upriseup.co.uk/careers/paid-digital-media-assistant/</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Paid Digital Media Analyst</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://upriseup.co.uk/careers/paid-digital-media-analyst/</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SEO Assistant</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://upriseup.co.uk/careers/seo-assistant/</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SEO Analyst</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Uprise Up</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://upriseup.co.uk/careers/seo-analyst/</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>News 21 September, 2026 HM Land Registry drives forward data modernisation programme with Version 1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Version 1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://www.version1.com/news/hm-land-registry-drives-forward-data-modernisation-programme-with-version-1/</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Trainee Social Media Assistant</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Netcom Online Learning</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://www.reed.co.uk/jobs/trainee-social-media-assistant/57500395</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Trainee Social Media Executive</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Netcom Online Learning</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.reed.co.uk/jobs/trainee-social-media-executive/57500406</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Trainee Social Media Specialist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Netcom Online Learning</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.reed.co.uk/jobs/trainee-social-media-specialist/57500398</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Part Time Marketing &amp; Design Executive</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Parkside Office Professional</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.reed.co.uk/jobs/part-time-marketing-design-executive/57479018</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Trainee Digital Marketing Executive</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ITOL Recruit</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.reed.co.uk/jobs/trainee-digital-marketing-executive/57482906</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Spanish and Japanese Sales Account Executive</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>People First</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.reed.co.uk/jobs/spanish-and-japanese-sales-account-executive/57480189</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Account Executive - SAAS / Enterprise - B2B - Global Fintech Sector..</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hawke Search </t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.reed.co.uk/jobs/account-executive-saas-enterprise-b2b-global-fintech-sector/57482672</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>New Business Account Executive – MSPS, Outsourced Service, Integration Services, Service Based SaaS.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Global Technology Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.reed.co.uk/jobs/new-business-account-executive--msps-outsourced-service-integration-services-service-based-saas/57487256</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Assistant, Digital Sales and Marketing</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Fifth Season</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940234757?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Agency New Business Executive (Digital Marketing)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Awin</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931112462?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Trading Performance Analyst - Hospitals &amp; Primary Care</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Nuffield Health</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936270512?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CIBSE Certification Marketing Executive</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Cibse</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5940251788?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Social Media Executive - Training Course</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Netcom Training</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5938299681?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Freelance Social Media &amp; Marketing Executive</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>StudioXAG</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5939062483?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Interim Marketing Coordinator</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Frasers Hospitality</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5945045489?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Temporary Marketing Assistant</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Michael Page</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936932882?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Trainee Sales &amp; Marketing Assistant</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Horizon</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5930698734?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Marketing Assistant - No Experience Required</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Growth for Good</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5934612226?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Account Executive, Media Sales</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Blis</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5942325792?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>New Business Executive at United Media</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>United Media</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5937643216?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Marketing Executive (12M Fixed Term Contract)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Enra Specialist Finance</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5931443469?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>PT Data Analysis &amp; Marketing/Sales Intern</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Bosch Group</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.co.uk/jobs/details/5936256509?utm_medium=api&amp;utm_source=50c0f0cd</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
@@ -7657,7 +7413,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="3">
@@ -7708,7 +7464,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>icims</t>
+          <t>jibe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7717,7 +7473,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6">
@@ -7853,11 +7609,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error: ReadTimeout: HTTPSConnectionPool(host='adsmithdigital.co.uk', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8237,7 +7993,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -8293,7 +8049,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error: HTTPError: 404 Client Error: Not Found for url: https://crucible.io/working-at-crucible/</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -8457,7 +8213,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43">
@@ -8657,7 +8413,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53">
@@ -9197,7 +8953,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -9217,7 +8973,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81">
@@ -9277,7 +9033,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
@@ -10457,7 +10213,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="143">
@@ -10477,7 +10233,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="144">
@@ -10557,7 +10313,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148">
@@ -10617,7 +10373,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151">
@@ -10777,7 +10533,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="159">
